--- a/data/trans_dic/P23_R2-Clase-trans_dic.xlsx
+++ b/data/trans_dic/P23_R2-Clase-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que fuma tabaco actualmente, de forma diaria o puntual</t>
+          <t>Población que fuma tabaco actualmente, de forma diaria o puntual (tasa de respuesta: 99,94%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>26,72; 35,56</t>
+          <t>27,22; 35,35</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>27,56; 37,41</t>
+          <t>27,78; 37,82</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>20,71; 29,23</t>
+          <t>20,76; 29,62</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>13,74; 20,45</t>
+          <t>13,45; 20,6</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>23,19; 33,08</t>
+          <t>23,43; 33,69</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>25,29; 35,6</t>
+          <t>25,08; 35,92</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>15,12; 23,9</t>
+          <t>15,51; 23,73</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>12,83; 18,62</t>
+          <t>12,88; 18,51</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>26,83; 33,44</t>
+          <t>26,59; 33,2</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>28,09; 35,41</t>
+          <t>27,78; 34,91</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>19,56; 25,88</t>
+          <t>19,38; 25,45</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>13,99; 18,68</t>
+          <t>14,19; 18,9</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>29,83; 39,84</t>
+          <t>29,85; 39,9</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>29,88; 39,86</t>
+          <t>29,94; 39,32</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>23,71; 32,87</t>
+          <t>23,63; 32,94</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>16,76; 24,74</t>
+          <t>16,99; 25,41</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>30,37; 40,09</t>
+          <t>30,31; 40,57</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>31,63; 42,45</t>
+          <t>31,3; 42,39</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>22,47; 32,14</t>
+          <t>22,2; 31,88</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>18,64; 26,3</t>
+          <t>18,32; 25,87</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>31,24; 38,58</t>
+          <t>31,04; 38,26</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>31,73; 39,49</t>
+          <t>32,07; 39,41</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>24,15; 31,0</t>
+          <t>24,21; 30,81</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>18,37; 23,93</t>
+          <t>18,29; 23,81</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>40,78; 49,79</t>
+          <t>41,07; 49,45</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>36,03; 44,15</t>
+          <t>36,19; 44,34</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>37,07; 46,23</t>
+          <t>37,28; 46,1</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>6,78; 29,9</t>
+          <t>7,51; 30,38</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>20,04; 33,42</t>
+          <t>20,07; 33,37</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>26,27; 38,22</t>
+          <t>26,3; 38,11</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>24,93; 39,29</t>
+          <t>24,41; 39,93</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>11,51; 20,54</t>
+          <t>11,22; 20,09</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>37,09; 44,67</t>
+          <t>37,16; 44,37</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>34,25; 41,15</t>
+          <t>34,15; 41,19</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>35,41; 42,84</t>
+          <t>35,43; 43,3</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>7,37; 25,41</t>
+          <t>9,11; 25,64</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>39,87; 45,38</t>
+          <t>40,24; 45,83</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>37,53; 43,38</t>
+          <t>37,14; 43,04</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>34,53; 40,17</t>
+          <t>34,41; 40,42</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>29,18; 35,97</t>
+          <t>29,25; 36,23</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>28,64; 35,35</t>
+          <t>28,19; 35,17</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>33,2; 40,5</t>
+          <t>33,14; 40,45</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>34,96; 41,59</t>
+          <t>35,0; 41,74</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>12,31; 28,62</t>
+          <t>10,9; 28,53</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>36,58; 40,91</t>
+          <t>36,52; 40,97</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>36,54; 41,24</t>
+          <t>36,62; 41,3</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>35,64; 39,94</t>
+          <t>35,62; 40,02</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>18,48; 31,33</t>
+          <t>17,34; 31,36</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>43,16; 54,06</t>
+          <t>43,02; 53,84</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>35,22; 44,48</t>
+          <t>35,46; 44,33</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>35,07; 42,8</t>
+          <t>34,97; 43,04</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>29,1; 38,56</t>
+          <t>28,98; 38,21</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>26,94; 34,93</t>
+          <t>26,89; 34,78</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>24,81; 31,63</t>
+          <t>25,15; 31,87</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>26,09; 32,86</t>
+          <t>26,0; 32,78</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>14,24; 22,15</t>
+          <t>14,36; 22,26</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>34,08; 40,81</t>
+          <t>33,91; 40,97</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>29,97; 35,35</t>
+          <t>30,23; 35,76</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>31,19; 36,46</t>
+          <t>31,2; 36,18</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>19,75; 27,04</t>
+          <t>20,01; 27,21</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>22,52; 32,77</t>
+          <t>22,44; 32,62</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>15,44; 25,1</t>
+          <t>15,1; 25,01</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>20,3; 31,04</t>
+          <t>20,1; 30,62</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>7,01; 21,42</t>
+          <t>5,78; 20,4</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>11,39; 15,18</t>
+          <t>11,58; 15,42</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>12,34; 16,48</t>
+          <t>12,29; 16,52</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>13,93; 18,39</t>
+          <t>13,59; 18,55</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>9,1; 13,8</t>
+          <t>9,29; 14,04</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>14,27; 17,89</t>
+          <t>14,28; 17,95</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>13,54; 17,19</t>
+          <t>13,41; 17,17</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>15,85; 20,0</t>
+          <t>15,77; 20,11</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>9,27; 14,26</t>
+          <t>9,28; 14,22</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>38,07; 41,61</t>
+          <t>38,11; 41,58</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>35,12; 38,65</t>
+          <t>35,21; 38,66</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>33,09; 36,37</t>
+          <t>32,95; 36,42</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>18,92; 27,13</t>
+          <t>17,56; 26,99</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>23,16; 26,18</t>
+          <t>22,92; 25,88</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>25,44; 28,68</t>
+          <t>25,38; 28,59</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>24,78; 27,86</t>
+          <t>24,49; 27,57</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>14,44; 19,5</t>
+          <t>14,72; 19,54</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>30,91; 33,26</t>
+          <t>30,93; 33,27</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>30,65; 32,99</t>
+          <t>30,78; 33,14</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>29,07; 31,45</t>
+          <t>29,18; 31,41</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>17,76; 22,7</t>
+          <t>18,04; 22,68</t>
         </is>
       </c>
     </row>
@@ -1669,7 +1669,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que fuma tabaco actualmente, de forma diaria o puntual</t>
+          <t>Población que fuma tabaco actualmente, de forma diaria o puntual (tasa de respuesta: 99,94%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1927,62 +1927,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>126605; 168493</t>
+          <t>128941; 167484</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>120496; 163545</t>
+          <t>121463; 165337</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>88873; 125404</t>
+          <t>89092; 127090</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>69430; 103291</t>
+          <t>67970; 104086</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>71130; 101440</t>
+          <t>71863; 103330</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>79537; 111950</t>
+          <t>78880; 112950</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>52481; 82960</t>
+          <t>53839; 82368</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>57389; 83302</t>
+          <t>57619; 82842</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>209428; 261006</t>
+          <t>207538; 259078</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>211129; 266176</t>
+          <t>208841; 262372</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>151802; 200841</t>
+          <t>150389; 197527</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>133268; 177924</t>
+          <t>135218; 180077</t>
         </is>
       </c>
     </row>
@@ -2135,62 +2135,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>109474; 146173</t>
+          <t>109542; 146398</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>125138; 166946</t>
+          <t>125408; 164670</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>89197; 123656</t>
+          <t>88888; 123920</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>75813; 111866</t>
+          <t>76825; 114899</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>112954; 149078</t>
+          <t>112695; 150854</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>106917; 143499</t>
+          <t>105792; 143297</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>83402; 119324</t>
+          <t>82401; 118369</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>71298; 100615</t>
+          <t>70101; 98977</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>230792; 285059</t>
+          <t>229341; 282664</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>240123; 298886</t>
+          <t>242700; 298289</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>180516; 231657</t>
+          <t>180979; 230292</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>153353; 199748</t>
+          <t>152685; 198784</t>
         </is>
       </c>
     </row>
@@ -2343,62 +2343,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>221166; 270042</t>
+          <t>222737; 268219</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>226758; 277876</t>
+          <t>227801; 279092</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>193497; 241300</t>
+          <t>194585; 240601</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>45281; 199836</t>
+          <t>50170; 203009</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>33622; 56071</t>
+          <t>33667; 55986</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>68342; 99431</t>
+          <t>68413; 99124</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>41407; 65269</t>
+          <t>40545; 66328</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>19206; 34286</t>
+          <t>18727; 33531</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>263376; 317229</t>
+          <t>263930; 315102</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>304710; 366015</t>
+          <t>303821; 366364</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>243660; 294742</t>
+          <t>243796; 297949</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>61589; 212240</t>
+          <t>76096; 214137</t>
         </is>
       </c>
     </row>
@@ -2551,62 +2551,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>493663; 562018</t>
+          <t>498361; 567586</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>434646; 502378</t>
+          <t>430030; 498395</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>396635; 461436</t>
+          <t>395236; 464370</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>301914; 372254</t>
+          <t>302702; 374876</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>204601; 252465</t>
+          <t>201342; 251249</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>254175; 310129</t>
+          <t>253722; 309694</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>288381; 343131</t>
+          <t>288694; 344372</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>120307; 279731</t>
+          <t>106548; 278875</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>714301; 798786</t>
+          <t>713033; 799986</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>702947; 793352</t>
+          <t>704464; 794417</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>703424; 788286</t>
+          <t>703002; 789920</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>371811; 630452</t>
+          <t>348963; 630951</t>
         </is>
       </c>
     </row>
@@ -2759,62 +2759,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>151302; 189517</t>
+          <t>150811; 188724</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>179826; 227089</t>
+          <t>181082; 226362</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>217673; 265690</t>
+          <t>217059; 267129</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>137937; 182763</t>
+          <t>137367; 181140</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>153240; 198689</t>
+          <t>152923; 197827</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>188698; 240533</t>
+          <t>191284; 242376</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>192356; 242214</t>
+          <t>191632; 241617</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>119686; 186185</t>
+          <t>120705; 187122</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>313331; 375197</t>
+          <t>311770; 376679</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>380933; 449384</t>
+          <t>384276; 454562</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>423574; 495037</t>
+          <t>423617; 491331</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>259615; 355536</t>
+          <t>263009; 357680</t>
         </is>
       </c>
     </row>
@@ -2967,62 +2967,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>66912; 97393</t>
+          <t>66680; 96921</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>41203; 66998</t>
+          <t>40294; 66750</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>58277; 89135</t>
+          <t>57717; 87936</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>16799; 51293</t>
+          <t>13852; 48860</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>142270; 189561</t>
+          <t>144606; 192534</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>136930; 182863</t>
+          <t>136311; 183319</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>150392; 198583</t>
+          <t>146775; 200319</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>69307; 105038</t>
+          <t>70758; 106932</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>220598; 276535</t>
+          <t>220818; 277433</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>186291; 236532</t>
+          <t>184592; 236247</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>216633; 273373</t>
+          <t>215497; 274893</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>92772; 142682</t>
+          <t>92873; 142299</t>
         </is>
       </c>
     </row>
@@ -3175,62 +3175,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>1244566; 1360393</t>
+          <t>1245912; 1359202</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>1201337; 1322118</t>
+          <t>1204633; 1322620</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>1119772; 1230762</t>
+          <t>1114959; 1232237</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>638398; 915271</t>
+          <t>592456; 910701</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>782346; 884239</t>
+          <t>774418; 874238</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>902534; 1017702</t>
+          <t>900642; 1014551</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>873807; 982243</t>
+          <t>863563; 972091</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>516389; 697232</t>
+          <t>526310; 698694</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>2054883; 2210608</t>
+          <t>2055773; 2211750</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>2136229; 2299280</t>
+          <t>2145018; 2309708</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>2008379; 2173519</t>
+          <t>2016271; 2170113</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>1234298; 1577745</t>
+          <t>1253799; 1576625</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P23_R2-Clase-trans_dic.xlsx
+++ b/data/trans_dic/P23_R2-Clase-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>16,8%</t>
+          <t>17,12%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>15,46%</t>
+          <t>14,98%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>16,17%</t>
+          <t>16,12%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>27,22; 35,35</t>
+          <t>27,32; 35,9</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>27,78; 37,82</t>
+          <t>27,82; 37,31</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>20,76; 29,62</t>
+          <t>20,76; 29,47</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>13,45; 20,6</t>
+          <t>14,0; 20,72</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>23,43; 33,69</t>
+          <t>23,31; 33,74</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>25,08; 35,92</t>
+          <t>24,98; 36,04</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>15,51; 23,73</t>
+          <t>15,43; 24,12</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>12,88; 18,51</t>
+          <t>12,49; 17,99</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>26,59; 33,2</t>
+          <t>26,74; 33,36</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>27,78; 34,91</t>
+          <t>27,87; 35,17</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>19,38; 25,45</t>
+          <t>19,35; 25,73</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>14,19; 18,9</t>
+          <t>14,02; 18,17</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>20,5%</t>
+          <t>19,62%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>21,8%</t>
+          <t>21,86%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>21,1%</t>
+          <t>20,67%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>29,85; 39,9</t>
+          <t>29,51; 39,56</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>29,94; 39,32</t>
+          <t>29,36; 39,72</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>23,63; 32,94</t>
+          <t>23,21; 33,42</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>16,99; 25,41</t>
+          <t>16,27; 24,22</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>30,31; 40,57</t>
+          <t>30,07; 40,06</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>31,3; 42,39</t>
+          <t>31,06; 42,12</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>22,2; 31,88</t>
+          <t>22,93; 31,97</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>18,32; 25,87</t>
+          <t>18,51; 25,38</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>31,04; 38,26</t>
+          <t>31,4; 38,54</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>32,07; 39,41</t>
+          <t>31,75; 38,93</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>24,21; 30,81</t>
+          <t>24,39; 31,14</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>18,29; 23,81</t>
+          <t>17,96; 23,44</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>17,97%</t>
+          <t>27,06%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>15,27%</t>
+          <t>14,58%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>17,43%</t>
+          <t>23,51%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>41,07; 49,45</t>
+          <t>40,93; 49,63</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>36,19; 44,34</t>
+          <t>36,44; 44,51</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>37,28; 46,1</t>
+          <t>37,39; 46,17</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>7,51; 30,38</t>
+          <t>22,78; 31,2</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>20,07; 33,37</t>
+          <t>19,95; 33,3</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>26,3; 38,11</t>
+          <t>26,35; 37,6</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>24,41; 39,93</t>
+          <t>24,79; 39,19</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>11,22; 20,09</t>
+          <t>10,7; 19,52</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>37,16; 44,37</t>
+          <t>37,24; 44,82</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>34,15; 41,19</t>
+          <t>34,48; 40,88</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>35,43; 43,3</t>
+          <t>35,29; 42,99</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>9,11; 25,64</t>
+          <t>20,15; 26,75</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>32,71%</t>
+          <t>32,1%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>21,92%</t>
+          <t>26,92%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>27,47%</t>
+          <t>29,86%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>40,24; 45,83</t>
+          <t>39,99; 45,69</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>37,14; 43,04</t>
+          <t>37,5; 43,27</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>34,41; 40,42</t>
+          <t>34,68; 40,46</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>29,25; 36,23</t>
+          <t>29,07; 35,42</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>28,19; 35,17</t>
+          <t>28,88; 35,64</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>33,14; 40,45</t>
+          <t>33,24; 40,62</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>35,0; 41,74</t>
+          <t>35,05; 41,65</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>10,9; 28,53</t>
+          <t>24,15; 29,78</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>36,52; 40,97</t>
+          <t>36,58; 41,08</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>36,62; 41,3</t>
+          <t>36,42; 41,08</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>35,62; 40,02</t>
+          <t>35,72; 39,96</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>17,34; 31,36</t>
+          <t>27,69; 31,85</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>33,48%</t>
+          <t>32,39%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>18,88%</t>
+          <t>20,97%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>24,14%</t>
+          <t>25,6%</t>
         </is>
       </c>
     </row>
@@ -1277,69 +1277,69 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>43,02; 53,84</t>
+          <t>43,32; 53,88</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>35,46; 44,33</t>
+          <t>35,35; 44,11</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>34,97; 43,04</t>
+          <t>35,28; 42,79</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>28,98; 38,21</t>
+          <t>27,98; 37,05</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>26,89; 34,78</t>
+          <t>26,62; 34,6</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>25,15; 31,87</t>
+          <t>24,64; 31,91</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>26,0; 32,78</t>
+          <t>26,25; 33,0</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>14,36; 22,26</t>
+          <t>18,61; 23,52</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>33,91; 40,97</t>
+          <t>34,28; 40,55</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>30,23; 35,76</t>
+          <t>30,13; 35,46</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>31,2; 36,18</t>
+          <t>31,08; 36,19</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>20,01; 27,21</t>
+          <t>23,24; 27,97</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1364,7 +1364,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>12,14%</t>
+          <t>11,43%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>11,3%</t>
+          <t>10,85%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>11,5%</t>
+          <t>10,97%</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>22,44; 32,62</t>
+          <t>22,33; 32,31</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>15,1; 25,01</t>
+          <t>14,68; 24,71</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>20,1; 30,62</t>
+          <t>19,74; 30,28</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>5,78; 20,4</t>
+          <t>6,27; 18,59</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>11,58; 15,42</t>
+          <t>11,64; 15,25</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>12,29; 16,52</t>
+          <t>12,19; 16,46</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>13,59; 18,55</t>
+          <t>13,85; 18,13</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>9,29; 14,04</t>
+          <t>9,05; 13,57</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>14,28; 17,95</t>
+          <t>14,21; 18,19</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>13,41; 17,17</t>
+          <t>13,43; 17,32</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>15,77; 20,11</t>
+          <t>15,83; 19,98</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>9,28; 14,22</t>
+          <t>9,05; 13,61</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>24,42%</t>
+          <t>25,89%</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1524,7 +1524,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>17,81%</t>
+          <t>19,0%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>21,02%</t>
+          <t>22,35%</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>38,11; 41,58</t>
+          <t>38,23; 41,53</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>35,21; 38,66</t>
+          <t>35,23; 38,58</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>32,95; 36,42</t>
+          <t>32,91; 36,12</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>17,56; 26,99</t>
+          <t>24,14; 27,71</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>22,92; 25,88</t>
+          <t>23,03; 25,93</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>25,38; 28,59</t>
+          <t>25,48; 28,63</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>24,49; 27,57</t>
+          <t>24,7; 27,68</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>14,72; 19,54</t>
+          <t>17,86; 20,27</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>30,93; 33,27</t>
+          <t>30,9; 33,18</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>30,78; 33,14</t>
+          <t>30,71; 33,08</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>29,18; 31,41</t>
+          <t>29,26; 31,52</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>18,04; 22,68</t>
+          <t>21,26; 23,3</t>
         </is>
       </c>
     </row>
@@ -1874,7 +1874,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>84892</t>
+          <t>94281</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>69178</t>
+          <t>73164</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1914,7 +1914,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>154070</t>
+          <t>167445</t>
         </is>
       </c>
     </row>
@@ -1927,62 +1927,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>128941; 167484</t>
+          <t>129442; 170095</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>121463; 165337</t>
+          <t>121631; 163116</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>89092; 127090</t>
+          <t>89073; 126450</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>67970; 104086</t>
+          <t>77077; 114103</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>71863; 103330</t>
+          <t>71494; 103475</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>78880; 112950</t>
+          <t>78559; 113324</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>53839; 82368</t>
+          <t>53546; 83710</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>57619; 82842</t>
+          <t>60990; 87864</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>207538; 259078</t>
+          <t>208657; 260391</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>208841; 262372</t>
+          <t>209499; 264352</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>150389; 197527</t>
+          <t>150202; 199719</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>135218; 180077</t>
+          <t>145718; 188805</t>
         </is>
       </c>
     </row>
@@ -2082,7 +2082,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>92717</t>
+          <t>94800</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2102,7 +2102,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>83405</t>
+          <t>92509</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2122,7 +2122,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>176122</t>
+          <t>187309</t>
         </is>
       </c>
     </row>
@@ -2135,62 +2135,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>109542; 146398</t>
+          <t>108284; 145173</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>125408; 164670</t>
+          <t>122941; 166327</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>88888; 123920</t>
+          <t>87291; 125692</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>76825; 114899</t>
+          <t>78621; 117053</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>112695; 150854</t>
+          <t>111817; 148972</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>105792; 143297</t>
+          <t>104982; 142378</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>82401; 118369</t>
+          <t>85114; 118682</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>70101; 98977</t>
+          <t>78342; 107381</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>229341; 282664</t>
+          <t>231989; 284717</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>242700; 298289</t>
+          <t>240310; 294662</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>180979; 230292</t>
+          <t>182302; 232708</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>152685; 198784</t>
+          <t>162799; 212462</t>
         </is>
       </c>
     </row>
@@ -2290,7 +2290,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>120061</t>
+          <t>127614</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2310,7 +2310,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>25492</t>
+          <t>27334</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2330,7 +2330,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>145553</t>
+          <t>154948</t>
         </is>
       </c>
     </row>
@@ -2343,62 +2343,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>222737; 268219</t>
+          <t>222015; 269167</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>227801; 279092</t>
+          <t>229349; 280140</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>194585; 240601</t>
+          <t>195167; 240983</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>50170; 203009</t>
+          <t>107448; 147130</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>33667; 55986</t>
+          <t>33477; 55868</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>68413; 99124</t>
+          <t>68535; 97803</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>40545; 66328</t>
+          <t>41179; 65103</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>18727; 33531</t>
+          <t>20066; 36601</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>263930; 315102</t>
+          <t>264471; 318289</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>303821; 366364</t>
+          <t>306699; 363676</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>243796; 297949</t>
+          <t>242817; 295807</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>76096; 214137</t>
+          <t>132833; 176301</t>
         </is>
       </c>
     </row>
@@ -2498,7 +2498,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>338478</t>
+          <t>363291</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2518,7 +2518,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>214255</t>
+          <t>231688</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2538,7 +2538,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>552733</t>
+          <t>594979</t>
         </is>
       </c>
     </row>
@@ -2551,62 +2551,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>498361; 567586</t>
+          <t>495158; 565750</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>430030; 498395</t>
+          <t>434296; 501064</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>395236; 464370</t>
+          <t>398423; 464749</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>302702; 374876</t>
+          <t>329077; 400874</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>201342; 251249</t>
+          <t>206312; 254544</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>253722; 309694</t>
+          <t>254476; 311048</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>288694; 344372</t>
+          <t>289140; 343617</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>106548; 278875</t>
+          <t>207828; 256293</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>713033; 799986</t>
+          <t>714322; 802105</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>704464; 794417</t>
+          <t>700549; 790289</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>703002; 789920</t>
+          <t>705088; 788656</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>348963; 630951</t>
+          <t>551603; 634569</t>
         </is>
       </c>
     </row>
@@ -2706,7 +2706,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>158697</t>
+          <t>183585</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>158679</t>
+          <t>174095</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2746,7 +2746,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>317376</t>
+          <t>357680</t>
         </is>
       </c>
     </row>
@@ -2759,69 +2759,69 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>150811; 188724</t>
+          <t>151849; 188891</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>181082; 226362</t>
+          <t>180506; 225208</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>217059; 267129</t>
+          <t>218970; 265608</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>137367; 181140</t>
+          <t>158600; 210013</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>152923; 197827</t>
+          <t>151409; 196765</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>191284; 242376</t>
+          <t>187401; 242690</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>191632; 241617</t>
+          <t>193473; 243265</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>120705; 187122</t>
+          <t>154471; 195285</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>311770; 376679</t>
+          <t>315130; 372791</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>384276; 454562</t>
+          <t>382966; 450685</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>423617; 491331</t>
+          <t>421991; 491431</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>263009; 357680</t>
+          <t>324688; 390681</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -2914,7 +2914,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>29079</t>
+          <t>26975</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2934,7 +2934,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>86052</t>
+          <t>91571</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -2954,7 +2954,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>115131</t>
+          <t>118546</t>
         </is>
       </c>
     </row>
@@ -2967,62 +2967,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>66680; 96921</t>
+          <t>66348; 96007</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>40294; 66750</t>
+          <t>39190; 65942</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>57717; 87936</t>
+          <t>56681; 86942</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>13852; 48860</t>
+          <t>14802; 43894</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>144606; 192534</t>
+          <t>145318; 190442</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>136311; 183319</t>
+          <t>135259; 182589</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>146775; 200319</t>
+          <t>149532; 195683</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>70758; 106932</t>
+          <t>76411; 114552</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>220818; 277433</t>
+          <t>219723; 281152</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>184592; 236247</t>
+          <t>184812; 238402</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>215497; 274893</t>
+          <t>216369; 273059</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>92873; 142299</t>
+          <t>97785; 147022</t>
         </is>
       </c>
     </row>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>823924</t>
+          <t>890545</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -3142,7 +3142,7 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>637061</t>
+          <t>690361</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3162,7 +3162,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>1460985</t>
+          <t>1580906</t>
         </is>
       </c>
     </row>
@@ -3175,62 +3175,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>1245912; 1359202</t>
+          <t>1249875; 1357754</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>1204633; 1322620</t>
+          <t>1205138; 1319841</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>1114959; 1232237</t>
+          <t>1113595; 1222223</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>592456; 910701</t>
+          <t>830345; 953171</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>774418; 874238</t>
+          <t>777890; 875875</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>900642; 1014551</t>
+          <t>903959; 1015863</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>863563; 972091</t>
+          <t>870872; 975934</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>526310; 698694</t>
+          <t>648871; 736605</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>2055773; 2211750</t>
+          <t>2054238; 2205661</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>2145018; 2309708</t>
+          <t>2139883; 2305412</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>2016271; 2170113</t>
+          <t>2022076; 2177737</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>1253799; 1576625</t>
+          <t>1503780; 1648576</t>
         </is>
       </c>
     </row>
